--- a/school_lublino/vor_lublino_ceiling.xlsx
+++ b/school_lublino/vor_lublino_ceiling.xlsx
@@ -9,19 +9,21 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" activeTab="2"/>
+    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ВОР 2 э. шт." sheetId="8" r:id="rId1"/>
     <sheet name="Спец 2 э. шт." sheetId="7" r:id="rId2"/>
     <sheet name="Спец 2 эт. шлиф." sheetId="9" r:id="rId3"/>
+    <sheet name="1этВор" sheetId="10" r:id="rId4"/>
+    <sheet name="1эт спец" sheetId="11" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="123">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -306,6 +308,93 @@
   </si>
   <si>
     <t>Итог:</t>
+  </si>
+  <si>
+    <t>Ведомость работ и используемых материалов</t>
+  </si>
+  <si>
+    <t>Шлифование бетонных поверхностей</t>
+  </si>
+  <si>
+    <t>м²</t>
+  </si>
+  <si>
+    <t>Штукатурка цементным составом толщиной 21-40 мм</t>
+  </si>
+  <si>
+    <t>Грунтовка универсальный ЛАСТИМИН / LP-51 А</t>
+  </si>
+  <si>
+    <t>Штукатурка цементная</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>Сетка штукатурная стеклопакетная 10х10 мм</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>Профиль углозащитный оцинкованный 31х31 мм 0,5 мм</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> п.м</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности потолка СКБ</t>
+  </si>
+  <si>
+    <t>Шпатлевка гипсовая белая</t>
+  </si>
+  <si>
+    <t>Грунт универсальный ЛАСТИМИН</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ</t>
+  </si>
+  <si>
+    <t>1.045, 1.046</t>
+  </si>
+  <si>
+    <t>1.053, 1.054</t>
+  </si>
+  <si>
+    <t>1.039</t>
+  </si>
+  <si>
+    <t>1.038</t>
+  </si>
+  <si>
+    <t>1.037</t>
+  </si>
+  <si>
+    <t>1.036</t>
+  </si>
+  <si>
+    <t>1.035</t>
+  </si>
+  <si>
+    <t>1.034</t>
+  </si>
+  <si>
+    <t>1.026</t>
+  </si>
+  <si>
+    <t>60.41 п.м.</t>
+  </si>
+  <si>
+    <t>51.28 п.м.</t>
+  </si>
+  <si>
+    <t>П-9.1</t>
+  </si>
+  <si>
+    <t>П-5</t>
+  </si>
+  <si>
+    <t>П-6, П-12</t>
   </si>
 </sst>
 </file>
@@ -315,7 +404,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,6 +446,27 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -366,7 +476,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -611,12 +721,141 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -773,6 +1012,157 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -791,14 +1181,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1341,25 +1745,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="109" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
       <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="110" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="112"/>
       <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -2136,18 +2540,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
     </row>
     <row r="3" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -2156,7 +2560,7 @@
       <c r="B3" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="54" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2167,7 +2571,7 @@
       <c r="B4" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="60">
+      <c r="C4" s="54">
         <v>78.238</v>
       </c>
     </row>
@@ -2178,7 +2582,7 @@
       <c r="B5" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="60">
+      <c r="C5" s="54">
         <v>79.463999999999999</v>
       </c>
     </row>
@@ -2189,7 +2593,7 @@
       <c r="B6" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="60">
+      <c r="C6" s="54">
         <v>76.085999999999999</v>
       </c>
     </row>
@@ -2200,7 +2604,7 @@
       <c r="B7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="60">
+      <c r="C7" s="54">
         <v>171.64400000000001</v>
       </c>
     </row>
@@ -2211,7 +2615,7 @@
       <c r="B8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="60">
+      <c r="C8" s="54">
         <v>15.026</v>
       </c>
     </row>
@@ -2222,7 +2626,7 @@
       <c r="B9" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="60">
+      <c r="C9" s="54">
         <v>26.302500000000002</v>
       </c>
     </row>
@@ -2233,7 +2637,7 @@
       <c r="B10" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="60">
+      <c r="C10" s="54">
         <v>72.715000000000003</v>
       </c>
     </row>
@@ -2244,7 +2648,7 @@
       <c r="B11" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="60">
+      <c r="C11" s="54">
         <v>72.882999999999996</v>
       </c>
     </row>
@@ -2255,7 +2659,7 @@
       <c r="B12" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="60">
+      <c r="C12" s="54">
         <v>72.882999999999996</v>
       </c>
     </row>
@@ -2266,7 +2670,7 @@
       <c r="B13" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="60">
+      <c r="C13" s="54">
         <v>71.906499999999994</v>
       </c>
     </row>
@@ -2277,7 +2681,7 @@
       <c r="B14" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="60">
+      <c r="C14" s="54">
         <v>71.882999999999996</v>
       </c>
     </row>
@@ -2288,7 +2692,7 @@
       <c r="B15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="60">
+      <c r="C15" s="54">
         <v>162.11799999999999</v>
       </c>
     </row>
@@ -2299,7 +2703,7 @@
       <c r="B16" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="60">
+      <c r="C16" s="54">
         <v>72.882999999999996</v>
       </c>
     </row>
@@ -2310,7 +2714,7 @@
       <c r="B17" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="60">
+      <c r="C17" s="54">
         <v>18.909000000000002</v>
       </c>
     </row>
@@ -2321,7 +2725,7 @@
       <c r="B18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="60">
+      <c r="C18" s="54">
         <v>23.309000000000001</v>
       </c>
     </row>
@@ -2332,7 +2736,7 @@
       <c r="B19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="60">
+      <c r="C19" s="54">
         <v>6.3030000000000008</v>
       </c>
     </row>
@@ -2343,7 +2747,7 @@
       <c r="B20" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="60">
+      <c r="C20" s="54">
         <v>3.5309999999999997</v>
       </c>
     </row>
@@ -2354,7 +2758,7 @@
       <c r="B21" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="60">
+      <c r="C21" s="54">
         <v>87.295999999999992</v>
       </c>
     </row>
@@ -2365,7 +2769,7 @@
       <c r="B22" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="60">
+      <c r="C22" s="54">
         <v>160.84199999999998</v>
       </c>
     </row>
@@ -2376,7 +2780,7 @@
       <c r="B23" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="60">
+      <c r="C23" s="54">
         <v>59.191000000000003</v>
       </c>
     </row>
@@ -2387,7 +2791,7 @@
       <c r="B24" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="60">
+      <c r="C24" s="54">
         <v>28.035</v>
       </c>
     </row>
@@ -2398,7 +2802,7 @@
       <c r="B25" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="60">
+      <c r="C25" s="54">
         <v>23.48</v>
       </c>
     </row>
@@ -2409,7 +2813,7 @@
       <c r="B26" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="60">
+      <c r="C26" s="54">
         <v>28.181999999999999</v>
       </c>
     </row>
@@ -2420,7 +2824,7 @@
       <c r="B27" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="60">
+      <c r="C27" s="54">
         <v>20.433</v>
       </c>
     </row>
@@ -2431,7 +2835,7 @@
       <c r="B28" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="60">
+      <c r="C28" s="54">
         <v>10.752000000000001</v>
       </c>
     </row>
@@ -2442,7 +2846,7 @@
       <c r="B29" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="60">
+      <c r="C29" s="54">
         <v>6.6549999999999994</v>
       </c>
     </row>
@@ -2453,7 +2857,7 @@
       <c r="B30" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="60">
+      <c r="C30" s="54">
         <v>13.365</v>
       </c>
     </row>
@@ -2464,7 +2868,7 @@
       <c r="B31" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="60">
+      <c r="C31" s="54">
         <v>11.737</v>
       </c>
     </row>
@@ -2475,7 +2879,7 @@
       <c r="B32" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="60">
+      <c r="C32" s="54">
         <v>24.527999999999999</v>
       </c>
     </row>
@@ -2486,7 +2890,7 @@
       <c r="B33" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="60">
+      <c r="C33" s="54">
         <v>9.6689999999999987</v>
       </c>
     </row>
@@ -2497,7 +2901,7 @@
       <c r="B34" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="60">
+      <c r="C34" s="54">
         <v>15.718999999999999</v>
       </c>
     </row>
@@ -2508,7 +2912,7 @@
       <c r="B35" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="60">
+      <c r="C35" s="54">
         <v>22.144500000000001</v>
       </c>
     </row>
@@ -2519,7 +2923,7 @@
       <c r="B36" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="60">
+      <c r="C36" s="54">
         <v>8.7669999999999995</v>
       </c>
     </row>
@@ -2530,7 +2934,7 @@
       <c r="B37" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="60">
+      <c r="C37" s="54">
         <v>13.189</v>
       </c>
     </row>
@@ -2541,7 +2945,7 @@
       <c r="B38" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C38" s="60">
+      <c r="C38" s="54">
         <v>9.702</v>
       </c>
     </row>
@@ -2552,7 +2956,7 @@
       <c r="B39" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="60">
+      <c r="C39" s="54">
         <v>20.296499999999998</v>
       </c>
     </row>
@@ -2563,7 +2967,7 @@
       <c r="B40" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="60">
+      <c r="C40" s="54">
         <v>9.152000000000001</v>
       </c>
     </row>
@@ -2574,7 +2978,7 @@
       <c r="B41" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C41" s="60">
+      <c r="C41" s="54">
         <v>15.499000000000001</v>
       </c>
     </row>
@@ -2585,7 +2989,7 @@
       <c r="B42" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C42" s="60">
+      <c r="C42" s="54">
         <v>20.327999999999999</v>
       </c>
     </row>
@@ -2596,7 +3000,7 @@
       <c r="B43" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="60">
+      <c r="C43" s="54">
         <v>8.1300000000000008</v>
       </c>
     </row>
@@ -2607,7 +3011,7 @@
       <c r="B44" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="60">
+      <c r="C44" s="54">
         <v>16.894500000000001</v>
       </c>
     </row>
@@ -2618,7 +3022,7 @@
       <c r="B45" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C45" s="60">
+      <c r="C45" s="54">
         <v>34.702500000000001</v>
       </c>
     </row>
@@ -2629,7 +3033,7 @@
       <c r="B46" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C46" s="60">
+      <c r="C46" s="54">
         <v>76.272000000000006</v>
       </c>
     </row>
@@ -2640,16 +3044,16 @@
       <c r="B47" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C47" s="60">
+      <c r="C47" s="54">
         <v>8.4209999999999994</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="61"/>
-      <c r="B48" s="62" t="s">
+      <c r="A48" s="55"/>
+      <c r="B48" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="63">
+      <c r="C48" s="57">
         <f>SUM(C4:C47)</f>
         <v>1859.466000000001</v>
       </c>
@@ -2662,4 +3066,638 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="61" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="58"/>
+      <c r="B1" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="60"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="64"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="63" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="67" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="66"/>
+      <c r="E3" s="108">
+        <f>SUM('1эт спец'!D25+'1эт спец'!D23+'1эт спец'!D21+'1эт спец'!D19+'1эт спец'!D17+'1эт спец'!D15+'1эт спец'!D13+'1эт спец'!D8+'1эт спец'!D3)</f>
+        <v>1268.4699999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="69" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="69"/>
+      <c r="E4" s="70">
+        <v>58.519999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="75" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="73"/>
+      <c r="E5" s="74">
+        <f>E4*0.25</f>
+        <v>14.629999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="76" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="75" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="76"/>
+      <c r="E6" s="77">
+        <f>E4*0.15</f>
+        <v>8.7779999999999987</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="72" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="75" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="76"/>
+      <c r="E7" s="74">
+        <v>58.519999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="78" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="79" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="81" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="79"/>
+      <c r="E8" s="80">
+        <v>111.69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="68" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="69" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="69"/>
+      <c r="E9" s="70">
+        <v>1268.4699999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="72" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="75" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="76"/>
+      <c r="E10" s="77">
+        <f>E9*4.5</f>
+        <v>5708.1149999999989</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="78" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="79" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="83" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="79"/>
+      <c r="E11" s="82">
+        <f>E9*0.15</f>
+        <v>190.27049999999997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="116"/>
+      <c r="B13" s="117" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="118"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="119" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="118" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="120" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="121" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="122" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="119" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="115">
+        <v>1</v>
+      </c>
+      <c r="E15" s="77">
+        <f>E17</f>
+        <v>1268.4699999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="122" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="119" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="115">
+        <v>1</v>
+      </c>
+      <c r="E16" s="74">
+        <v>58.519999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="122" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="119" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="115">
+        <v>1</v>
+      </c>
+      <c r="E17" s="74">
+        <v>1268.4699999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="122" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="115">
+        <v>4.5</v>
+      </c>
+      <c r="E18" s="77">
+        <f>E17*4.5</f>
+        <v>5708.1149999999989</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="122" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="115">
+        <v>0.15</v>
+      </c>
+      <c r="E19" s="77">
+        <f>E17*0.15</f>
+        <v>190.27049999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="55.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="84"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="86" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="87"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="88" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="89" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="90" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="91" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="92">
+        <v>1</v>
+      </c>
+      <c r="B3" s="93" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="94" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="95">
+        <v>336.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="96"/>
+      <c r="B4" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="75">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="96"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="73" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="75">
+        <f>D4</f>
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="96"/>
+      <c r="B6" s="97"/>
+      <c r="C6" s="98" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="99" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="100"/>
+      <c r="B7" s="101"/>
+      <c r="C7" s="102" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="83">
+        <f>D3</f>
+        <v>336.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="103">
+        <v>2</v>
+      </c>
+      <c r="B8" s="104" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="105" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="71">
+        <v>543.35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="96"/>
+      <c r="B9" s="97" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="75">
+        <v>28.32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="96"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="73" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="75">
+        <f>D9</f>
+        <v>28.32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="96"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="98" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="99" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="100"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="102" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="83">
+        <f>D8</f>
+        <v>543.35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="103">
+        <v>3</v>
+      </c>
+      <c r="B13" s="106" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="105" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" s="71">
+        <v>143.85999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="100"/>
+      <c r="B14" s="107" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="102" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="83">
+        <f>D13</f>
+        <v>143.85999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="103">
+        <v>4</v>
+      </c>
+      <c r="B15" s="106" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="105" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="71">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="100"/>
+      <c r="B16" s="107" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="102" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="83">
+        <f>D15</f>
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="103">
+        <v>5</v>
+      </c>
+      <c r="B17" s="106" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="105" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="71">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="100"/>
+      <c r="B18" s="107" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="102" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="83">
+        <f>D17</f>
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="103">
+        <v>6</v>
+      </c>
+      <c r="B19" s="106" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="105" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="71">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="100"/>
+      <c r="B20" s="107" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="102" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="83">
+        <f>D19</f>
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="103">
+        <v>7</v>
+      </c>
+      <c r="B21" s="106" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="105" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="71">
+        <v>12.01</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="100"/>
+      <c r="B22" s="107" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="102" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="83">
+        <f>D21</f>
+        <v>12.01</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="103">
+        <v>8</v>
+      </c>
+      <c r="B23" s="106" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23" s="105" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="71">
+        <v>17.239999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="100"/>
+      <c r="B24" s="107" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="102" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" s="83">
+        <f>D23</f>
+        <v>17.239999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="103">
+        <v>9</v>
+      </c>
+      <c r="B25" s="106" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="105" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="71">
+        <v>192.38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="100"/>
+      <c r="B26" s="107" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="102" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="83">
+        <f>D25</f>
+        <v>192.38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/school_lublino/vor_lublino_ceiling.xlsx
+++ b/school_lublino/vor_lublino_ceiling.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" activeTab="3"/>
+    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" tabRatio="603" firstSheet="3" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="ВОР 2 э. шт." sheetId="8" r:id="rId1"/>
@@ -17,13 +17,17 @@
     <sheet name="Спец 2 эт. шлиф." sheetId="9" r:id="rId3"/>
     <sheet name="1этВор" sheetId="10" r:id="rId4"/>
     <sheet name="1эт спец" sheetId="11" r:id="rId5"/>
+    <sheet name="Вор2Вып" sheetId="12" r:id="rId6"/>
+    <sheet name="Общий" sheetId="13" r:id="rId7"/>
+    <sheet name="4.СКБвор" sheetId="15" r:id="rId8"/>
+    <sheet name="4.СКБспец" sheetId="14" r:id="rId9"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="133">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -395,6 +399,37 @@
   </si>
   <si>
     <t>П-6, П-12</t>
+  </si>
+  <si>
+    <t>Блок</t>
+  </si>
+  <si>
+    <t>№ пом.</t>
+  </si>
+  <si>
+    <t>Типы</t>
+  </si>
+  <si>
+    <t>Объем. м²</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>3.015; 3.016; 3.017; 3.018</t>
+  </si>
+  <si>
+    <t>3.077.2</t>
+  </si>
+  <si>
+    <t>сумма</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / потолка / ЖБ / 5 мм
+тип П-6, П-13, П-14, П-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ведомость работ и используемых материалов </t>
   </si>
 </sst>
 </file>
@@ -404,7 +439,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -467,6 +502,14 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -476,7 +519,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -850,12 +893,87 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1163,6 +1281,42 @@
     <xf numFmtId="2" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1181,34 +1335,85 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1219,6 +1424,79 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A2:E28" totalsRowShown="0" headerRowBorderDxfId="8" tableBorderDxfId="7">
+  <autoFilter ref="A2:E28">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="6"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState ref="A3:E28">
+    <sortCondition ref="D2:D28"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" name="№ п.п."/>
+    <tableColumn id="2" name="Блок"/>
+    <tableColumn id="3" name="№ пом." dataDxfId="6"/>
+    <tableColumn id="4" name="Типы"/>
+    <tableColumn id="5" name="Объем. м²"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица3" displayName="Таблица3" ref="A32:E76" totalsRowShown="0" headerRowBorderDxfId="5" tableBorderDxfId="4">
+  <autoFilter ref="A32:E76">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="6"/>
+        <filter val="13"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState ref="A36:E55">
+    <sortCondition ref="D32:D76"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" name="№ п.п."/>
+    <tableColumn id="2" name="Блок"/>
+    <tableColumn id="3" name="№ пом." dataDxfId="3"/>
+    <tableColumn id="4" name="Типы"/>
+    <tableColumn id="5" name="Объем. м²"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="A81:E106" totalsRowShown="0" headerRowBorderDxfId="2" tableBorderDxfId="1">
+  <autoFilter ref="A81:E106">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="13"/>
+        <filter val="14"/>
+        <filter val="16"/>
+        <filter val="6"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState ref="A82:E106">
+    <sortCondition ref="A81:A106"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" name="№ п.п."/>
+    <tableColumn id="2" name="Блок"/>
+    <tableColumn id="3" name="№ пом." dataDxfId="0"/>
+    <tableColumn id="4" name="Типы"/>
+    <tableColumn id="5" name="Объем. м²"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1745,25 +2023,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
       <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="124" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="112"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="126"/>
       <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -2540,18 +2818,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
     </row>
     <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
     </row>
     <row r="3" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -3241,42 +3519,42 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="116"/>
-      <c r="B13" s="117" t="s">
+      <c r="A13" s="110"/>
+      <c r="B13" s="111" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="118"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="117"/>
+      <c r="C13" s="112"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="116" t="s">
+      <c r="A14" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="119" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="118" t="s">
+      <c r="B14" s="113" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="120" t="s">
+      <c r="D14" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="121" t="s">
+      <c r="E14" s="115" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="122" t="s">
+      <c r="A15" s="116" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="119" t="s">
+      <c r="B15" s="113" t="s">
         <v>95</v>
       </c>
       <c r="C15" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="115">
+      <c r="D15" s="109">
         <v>1</v>
       </c>
       <c r="E15" s="77">
@@ -3285,16 +3563,16 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="122" t="s">
+      <c r="A16" s="116" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="119" t="s">
+      <c r="B16" s="113" t="s">
         <v>97</v>
       </c>
       <c r="C16" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="115">
+      <c r="D16" s="109">
         <v>1</v>
       </c>
       <c r="E16" s="74">
@@ -3302,16 +3580,16 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="122" t="s">
+      <c r="A17" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="119" t="s">
+      <c r="B17" s="113" t="s">
         <v>105</v>
       </c>
       <c r="C17" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="115">
+      <c r="D17" s="109">
         <v>1</v>
       </c>
       <c r="E17" s="74">
@@ -3319,7 +3597,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="122" t="s">
+      <c r="A18" s="116" t="s">
         <v>39</v>
       </c>
       <c r="B18" s="76" t="s">
@@ -3328,7 +3606,7 @@
       <c r="C18" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="115">
+      <c r="D18" s="109">
         <v>4.5</v>
       </c>
       <c r="E18" s="77">
@@ -3337,7 +3615,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="122" t="s">
+      <c r="A19" s="116" t="s">
         <v>40</v>
       </c>
       <c r="B19" s="76" t="s">
@@ -3346,7 +3624,7 @@
       <c r="C19" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="115">
+      <c r="D19" s="109">
         <v>0.15</v>
       </c>
       <c r="E19" s="77">
@@ -3700,4 +3978,2447 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:L106"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="120"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="10" width="9.140625" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="131"/>
+      <c r="G1" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="134"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="117" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="118" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="118" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="119" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2" s="117" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="118" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2" s="118" t="s">
+        <v>125</v>
+      </c>
+      <c r="J2" s="119" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="120">
+        <v>1.038</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>5.25</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C4" s="120">
+        <v>1.048</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>23.92</v>
+      </c>
+      <c r="F4">
+        <v>191.68</v>
+      </c>
+      <c r="H4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <v>23.92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="120">
+        <v>1.024</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>13.62</v>
+      </c>
+      <c r="F5">
+        <v>114.04</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>352.16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="120">
+        <v>1.026</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>191.68</v>
+      </c>
+      <c r="F6">
+        <v>68.81</v>
+      </c>
+      <c r="H6">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>762.49</v>
+      </c>
+      <c r="L6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="120">
+        <v>1.0389999999999999</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>149.69999999999999</v>
+      </c>
+      <c r="F7">
+        <v>68.81</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>38.21</v>
+      </c>
+      <c r="L7">
+        <f>--MID($L$6,IF(ROW(A1)=1,1,FIND("; ",$L$6,FIND("; ",$L$6,1)*(ROW(A1)-1))+2),FIND("; ",$L$6&amp;"; ",IF(ROW(A1)=1,1,FIND("; ",$L$6,FIND("; ",$L$6,1)*(ROW(A1)-1))+2))-IF(ROW(A1)=1,1,FIND("; ",$L$6,FIND("; ",$L$6,1)*(ROW(A1)-1))+2))</f>
+        <v>3.0150000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C8" s="120">
+        <v>1.0449999999999999</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>161.78</v>
+      </c>
+      <c r="F8">
+        <v>68.89</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>8</v>
+      </c>
+      <c r="J8">
+        <v>596.26</v>
+      </c>
+      <c r="L8">
+        <f t="shared" ref="L8:L19" si="0">--MID($L$6,IF(ROW(A2)=1,1,FIND("; ",$L$6,FIND("; ",$L$6,1)*(ROW(A2)-1))+2),FIND("; ",$L$6&amp;"; ",IF(ROW(A2)=1,1,FIND("; ",$L$6,FIND("; ",$L$6,1)*(ROW(A2)-1))+2))-IF(ROW(A2)=1,1,FIND("; ",$L$6,FIND("; ",$L$6,1)*(ROW(A2)-1))+2))</f>
+        <v>3.016</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C9" s="120">
+        <v>1.046</v>
+      </c>
+      <c r="D9">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>161.15</v>
+      </c>
+      <c r="F9">
+        <v>68.89</v>
+      </c>
+      <c r="H9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9">
+        <v>156.6</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="0"/>
+        <v>3.0169999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C10" s="120">
+        <v>1.0529999999999999</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>443.48</v>
+      </c>
+      <c r="F10">
+        <v>68.069999999999993</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
+      <c r="J10">
+        <v>46.57</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>3.0179999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="120">
+        <v>1.0269999999999999</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>114.04</v>
+      </c>
+      <c r="F11">
+        <v>139.1</v>
+      </c>
+      <c r="H11">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <v>296.76</v>
+      </c>
+      <c r="L11" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="120">
+        <v>1.028</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>68.81</v>
+      </c>
+      <c r="F12">
+        <v>17.22</v>
+      </c>
+      <c r="H12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I12">
+        <v>12</v>
+      </c>
+      <c r="J12">
+        <v>58.61</v>
+      </c>
+      <c r="L12" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="120">
+        <v>1.0289999999999999</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13">
+        <v>68.81</v>
+      </c>
+      <c r="F13">
+        <v>21.63</v>
+      </c>
+      <c r="L13" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="120">
+        <v>1.03</v>
+      </c>
+      <c r="D14">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>68.89</v>
+      </c>
+      <c r="F14">
+        <v>5.76</v>
+      </c>
+      <c r="L14" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="120">
+        <v>1.0309999999999999</v>
+      </c>
+      <c r="D15">
+        <v>8</v>
+      </c>
+      <c r="E15">
+        <v>68.89</v>
+      </c>
+      <c r="F15">
+        <v>3.34</v>
+      </c>
+      <c r="L15" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" s="120">
+        <v>1.032</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <v>68.069999999999993</v>
+      </c>
+      <c r="F16">
+        <v>5.25</v>
+      </c>
+      <c r="L16" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="120">
+        <v>1.0329999999999999</v>
+      </c>
+      <c r="D17">
+        <v>8</v>
+      </c>
+      <c r="E17">
+        <v>139.1</v>
+      </c>
+      <c r="L17" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C18" s="120">
+        <v>1.0489999999999999</v>
+      </c>
+      <c r="D18">
+        <v>8</v>
+      </c>
+      <c r="E18">
+        <v>103.8</v>
+      </c>
+      <c r="L18" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C19" s="120">
+        <v>1.05</v>
+      </c>
+      <c r="D19">
+        <v>8</v>
+      </c>
+      <c r="E19">
+        <v>22</v>
+      </c>
+      <c r="L19" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C20" s="120">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="D20">
+        <v>8</v>
+      </c>
+      <c r="E20">
+        <v>31.58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" s="120">
+        <v>1.034</v>
+      </c>
+      <c r="D21">
+        <v>9</v>
+      </c>
+      <c r="E21">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" s="120">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="D22">
+        <v>9</v>
+      </c>
+      <c r="E22">
+        <v>21.63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" s="120">
+        <v>1.036</v>
+      </c>
+      <c r="D23">
+        <v>9</v>
+      </c>
+      <c r="E23">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>19</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" s="120">
+        <v>1.0369999999999999</v>
+      </c>
+      <c r="D24">
+        <v>9</v>
+      </c>
+      <c r="E24">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C25" s="120">
+        <v>1.04</v>
+      </c>
+      <c r="D25">
+        <v>10</v>
+      </c>
+      <c r="E25">
+        <v>220.47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C26" s="120">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="D26">
+        <v>10</v>
+      </c>
+      <c r="E26">
+        <v>61.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C27" s="120">
+        <v>1.1439999999999999</v>
+      </c>
+      <c r="D27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C28">
+        <v>1.054</v>
+      </c>
+      <c r="D28">
+        <v>12</v>
+      </c>
+      <c r="E28">
+        <v>58.14</v>
+      </c>
+      <c r="F28" s="121"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="130"/>
+      <c r="C31" s="130"/>
+      <c r="D31" s="130"/>
+      <c r="E31" s="131"/>
+      <c r="G31" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="H31" s="133"/>
+      <c r="I31" s="133"/>
+      <c r="J31" s="134"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="117" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="118" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="118" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" s="119" t="s">
+        <v>126</v>
+      </c>
+      <c r="G32" s="117" t="s">
+        <v>0</v>
+      </c>
+      <c r="H32" s="118" t="s">
+        <v>123</v>
+      </c>
+      <c r="I32" s="118" t="s">
+        <v>125</v>
+      </c>
+      <c r="J32" s="119" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>28</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" s="120">
+        <v>2.0009999999999999</v>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33">
+        <v>73.55</v>
+      </c>
+      <c r="F33" s="120">
+        <v>1.0489999999999999</v>
+      </c>
+      <c r="H33">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I33">
+        <v>4</v>
+      </c>
+      <c r="J33">
+        <v>115.28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>27</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" s="120">
+        <v>2.0019999999999998</v>
+      </c>
+      <c r="D34">
+        <v>8</v>
+      </c>
+      <c r="E34">
+        <v>72.239999999999995</v>
+      </c>
+      <c r="F34" s="120">
+        <v>1.05</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>5</v>
+      </c>
+      <c r="J34">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>21</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" s="120">
+        <v>2.0030000000000001</v>
+      </c>
+      <c r="D35">
+        <v>8</v>
+      </c>
+      <c r="E35">
+        <v>68.260000000000005</v>
+      </c>
+      <c r="F35" s="120">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="H35">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I35">
+        <v>5</v>
+      </c>
+      <c r="J35">
+        <v>180.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>14</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" s="120">
+        <v>2.004</v>
+      </c>
+      <c r="D36">
+        <v>6</v>
+      </c>
+      <c r="E36">
+        <v>158.71</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>6</v>
+      </c>
+      <c r="J36">
+        <v>306.63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>43</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" s="120">
+        <v>2.0049999999999999</v>
+      </c>
+      <c r="D37">
+        <v>15</v>
+      </c>
+      <c r="E37">
+        <v>13.62</v>
+      </c>
+      <c r="H37">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I37">
+        <v>6</v>
+      </c>
+      <c r="J37">
+        <v>282.87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>23</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" s="120">
+        <v>2.0070000000000001</v>
+      </c>
+      <c r="D38">
+        <v>8</v>
+      </c>
+      <c r="E38">
+        <v>68.3</v>
+      </c>
+      <c r="H38">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I38">
+        <v>7</v>
+      </c>
+      <c r="J38">
+        <v>169.2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>26</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" s="120">
+        <v>2.008</v>
+      </c>
+      <c r="D39">
+        <v>8</v>
+      </c>
+      <c r="E39">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>8</v>
+      </c>
+      <c r="J39">
+        <v>625.16999999999996</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>25</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" s="120">
+        <v>2.0089999999999999</v>
+      </c>
+      <c r="D40">
+        <v>8</v>
+      </c>
+      <c r="E40">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>9</v>
+      </c>
+      <c r="J40">
+        <v>46.57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>20</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" s="120">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="D41">
+        <v>8</v>
+      </c>
+      <c r="E41">
+        <v>67.64</v>
+      </c>
+      <c r="H41">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I41">
+        <v>9</v>
+      </c>
+      <c r="J41">
+        <v>119.43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>24</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" s="120">
+        <v>2.0110000000000001</v>
+      </c>
+      <c r="D42">
+        <v>8</v>
+      </c>
+      <c r="E42">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="H42">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I42">
+        <v>13</v>
+      </c>
+      <c r="J42">
+        <v>299.02</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>15</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" s="120">
+        <v>2.012</v>
+      </c>
+      <c r="D43">
+        <v>6</v>
+      </c>
+      <c r="E43">
+        <v>149.25</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>15</v>
+      </c>
+      <c r="J43">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>22</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" s="120">
+        <v>2.0129999999999999</v>
+      </c>
+      <c r="D44">
+        <v>8</v>
+      </c>
+      <c r="E44">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="H44">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I44">
+        <v>15</v>
+      </c>
+      <c r="J44">
+        <v>8.0299999999999994</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>35</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" s="120">
+        <v>2.0139999999999998</v>
+      </c>
+      <c r="D45">
+        <v>9</v>
+      </c>
+      <c r="E45">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>34</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46" s="120">
+        <v>2.0150000000000001</v>
+      </c>
+      <c r="D46">
+        <v>9</v>
+      </c>
+      <c r="E46">
+        <v>21.87</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>33</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" s="120">
+        <v>2.016</v>
+      </c>
+      <c r="D47">
+        <v>9</v>
+      </c>
+      <c r="E47">
+        <v>5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>32</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48" s="120">
+        <v>2.0169999999999999</v>
+      </c>
+      <c r="D48">
+        <v>9</v>
+      </c>
+      <c r="E48">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>29</v>
+      </c>
+      <c r="B49">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C49" s="120">
+        <v>1.0489999999999999</v>
+      </c>
+      <c r="D49">
+        <v>8</v>
+      </c>
+      <c r="E49">
+        <v>67.98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>30</v>
+      </c>
+      <c r="B50">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C50" s="120">
+        <v>1.05</v>
+      </c>
+      <c r="D50">
+        <v>8</v>
+      </c>
+      <c r="E50">
+        <v>68.459999999999994</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>31</v>
+      </c>
+      <c r="B51">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C51" s="120">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="D51">
+        <v>8</v>
+      </c>
+      <c r="E51">
+        <v>113.65</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>17</v>
+      </c>
+      <c r="B52">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C52" s="120">
+        <v>2.0750000000000002</v>
+      </c>
+      <c r="D52">
+        <v>6</v>
+      </c>
+      <c r="E52">
+        <v>79.790000000000006</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>18</v>
+      </c>
+      <c r="B53">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C53" s="120">
+        <v>2.08</v>
+      </c>
+      <c r="D53">
+        <v>6</v>
+      </c>
+      <c r="E53">
+        <v>170.56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>16</v>
+      </c>
+      <c r="B54">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C54" s="120">
+        <v>2.0819999999999999</v>
+      </c>
+      <c r="D54">
+        <v>6</v>
+      </c>
+      <c r="E54">
+        <v>32.630000000000003</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>42</v>
+      </c>
+      <c r="B55">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C55" s="120">
+        <v>2.081</v>
+      </c>
+      <c r="D55">
+        <v>13</v>
+      </c>
+      <c r="E55">
+        <v>298.27999999999997</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>7</v>
+      </c>
+      <c r="B56">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C56" s="120">
+        <v>2.0840000000000001</v>
+      </c>
+      <c r="D56">
+        <v>5</v>
+      </c>
+      <c r="E56">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>19</v>
+      </c>
+      <c r="B57">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C57" s="120">
+        <v>2.085</v>
+      </c>
+      <c r="D57">
+        <v>7</v>
+      </c>
+      <c r="E57">
+        <v>168.62</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>6</v>
+      </c>
+      <c r="B58">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C58" s="120">
+        <v>2.0880000000000001</v>
+      </c>
+      <c r="D58">
+        <v>5</v>
+      </c>
+      <c r="E58">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>41</v>
+      </c>
+      <c r="B59">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C59" s="120">
+        <v>2.09</v>
+      </c>
+      <c r="D59">
+        <v>9</v>
+      </c>
+      <c r="E59">
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>40</v>
+      </c>
+      <c r="B60">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C60" s="120">
+        <v>2.0910000000000002</v>
+      </c>
+      <c r="D60">
+        <v>9</v>
+      </c>
+      <c r="E60">
+        <v>10.63</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>12</v>
+      </c>
+      <c r="B61">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C61" s="120">
+        <v>2.0939999999999999</v>
+      </c>
+      <c r="D61">
+        <v>5</v>
+      </c>
+      <c r="E61">
+        <v>23.36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>39</v>
+      </c>
+      <c r="B62">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C62" s="120">
+        <v>2.0950000000000002</v>
+      </c>
+      <c r="D62">
+        <v>9</v>
+      </c>
+      <c r="E62">
+        <v>8.7899999999999991</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>3</v>
+      </c>
+      <c r="B63">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C63" s="120">
+        <v>2.097</v>
+      </c>
+      <c r="D63">
+        <v>5</v>
+      </c>
+      <c r="E63">
+        <v>4.8499999999999996</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>4</v>
+      </c>
+      <c r="B64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C64" s="120">
+        <v>2.0979999999999999</v>
+      </c>
+      <c r="D64">
+        <v>5</v>
+      </c>
+      <c r="E64">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>11</v>
+      </c>
+      <c r="B65">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C65" s="120">
+        <v>2.0990000000000002</v>
+      </c>
+      <c r="D65">
+        <v>5</v>
+      </c>
+      <c r="E65">
+        <v>21.09</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>36</v>
+      </c>
+      <c r="B66">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C66" s="120">
+        <v>2.1</v>
+      </c>
+      <c r="D66">
+        <v>9</v>
+      </c>
+      <c r="E66">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>5</v>
+      </c>
+      <c r="B67">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C67" s="120">
+        <v>2.1019999999999999</v>
+      </c>
+      <c r="D67">
+        <v>5</v>
+      </c>
+      <c r="E67">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>10</v>
+      </c>
+      <c r="B68">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C68" s="120">
+        <v>2.1030000000000002</v>
+      </c>
+      <c r="D68">
+        <v>5</v>
+      </c>
+      <c r="E68">
+        <v>19.329999999999998</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>38</v>
+      </c>
+      <c r="B69">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C69" s="120">
+        <v>2.1040000000000001</v>
+      </c>
+      <c r="D69">
+        <v>9</v>
+      </c>
+      <c r="E69">
+        <v>8.4499999999999993</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>9</v>
+      </c>
+      <c r="B70">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C70" s="120">
+        <v>2.1059999999999999</v>
+      </c>
+      <c r="D70">
+        <v>5</v>
+      </c>
+      <c r="E70">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>37</v>
+      </c>
+      <c r="B71">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C71" s="120">
+        <v>2.1070000000000002</v>
+      </c>
+      <c r="D71">
+        <v>9</v>
+      </c>
+      <c r="E71">
+        <v>8.14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>13</v>
+      </c>
+      <c r="B72">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C72" s="120">
+        <v>2.109</v>
+      </c>
+      <c r="D72">
+        <v>5</v>
+      </c>
+      <c r="E72">
+        <v>33.049999999999997</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>1</v>
+      </c>
+      <c r="B73">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C73" s="120">
+        <v>2.16</v>
+      </c>
+      <c r="D73">
+        <v>4</v>
+      </c>
+      <c r="E73">
+        <v>72.64</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74" s="120">
+        <v>2.1619999999999999</v>
+      </c>
+      <c r="D74">
+        <v>5</v>
+      </c>
+      <c r="E74">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>8</v>
+      </c>
+      <c r="B75">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C75" s="120">
+        <v>2.1619999999999999</v>
+      </c>
+      <c r="D75">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>44</v>
+      </c>
+      <c r="B76">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C76" s="120">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="D76">
+        <v>15</v>
+      </c>
+      <c r="E76">
+        <v>8.02</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="B80" s="130"/>
+      <c r="C80" s="130"/>
+      <c r="D80" s="130"/>
+      <c r="E80" s="131"/>
+      <c r="G80" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="H80" s="133"/>
+      <c r="I80" s="133"/>
+      <c r="J80" s="134"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="117" t="s">
+        <v>0</v>
+      </c>
+      <c r="B81" s="118" t="s">
+        <v>123</v>
+      </c>
+      <c r="C81" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="D81" s="118" t="s">
+        <v>125</v>
+      </c>
+      <c r="E81" s="119" t="s">
+        <v>126</v>
+      </c>
+      <c r="G81" s="117" t="s">
+        <v>0</v>
+      </c>
+      <c r="H81" s="118" t="s">
+        <v>123</v>
+      </c>
+      <c r="I81" s="118" t="s">
+        <v>125</v>
+      </c>
+      <c r="J81" s="119" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>1</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82" s="120">
+        <v>3.0920000000000001</v>
+      </c>
+      <c r="D82">
+        <v>5</v>
+      </c>
+      <c r="E82">
+        <v>5.24</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82">
+        <v>5</v>
+      </c>
+      <c r="J82">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>2</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83" s="120">
+        <v>3.0139999999999998</v>
+      </c>
+      <c r="D83">
+        <v>6</v>
+      </c>
+      <c r="E83">
+        <v>148.61000000000001</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="I83">
+        <v>6</v>
+      </c>
+      <c r="J83">
+        <v>388.9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>3</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84" s="120">
+        <v>3.0049999999999999</v>
+      </c>
+      <c r="D84">
+        <v>6</v>
+      </c>
+      <c r="E84">
+        <v>239.62</v>
+      </c>
+      <c r="H84">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I84">
+        <v>6</v>
+      </c>
+      <c r="J84">
+        <v>380.9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>4</v>
+      </c>
+      <c r="B85">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C85" s="120">
+        <v>3.02</v>
+      </c>
+      <c r="D85">
+        <v>6</v>
+      </c>
+      <c r="E85">
+        <v>137.72999999999999</v>
+      </c>
+      <c r="H85">
+        <v>1</v>
+      </c>
+      <c r="I85">
+        <v>8</v>
+      </c>
+      <c r="J85">
+        <v>748.81</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>5</v>
+      </c>
+      <c r="B86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C86">
+        <v>3.0190000000000001</v>
+      </c>
+      <c r="D86">
+        <v>6</v>
+      </c>
+      <c r="E86">
+        <v>244.28</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86">
+        <v>9</v>
+      </c>
+      <c r="J86">
+        <v>46.57</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>6</v>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87" s="120">
+        <v>3.0110000000000001</v>
+      </c>
+      <c r="D87">
+        <v>8</v>
+      </c>
+      <c r="E87">
+        <v>67.14</v>
+      </c>
+      <c r="H87">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I87">
+        <v>13</v>
+      </c>
+      <c r="J87">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>7</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88" s="120">
+        <v>3.004</v>
+      </c>
+      <c r="D88">
+        <v>8</v>
+      </c>
+      <c r="E88">
+        <v>67.59</v>
+      </c>
+      <c r="H88">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I88">
+        <v>14</v>
+      </c>
+      <c r="J88">
+        <v>134.78</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>8</v>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89" s="120">
+        <v>3.008</v>
+      </c>
+      <c r="D89">
+        <v>8</v>
+      </c>
+      <c r="E89">
+        <v>67.84</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="I89">
+        <v>15</v>
+      </c>
+      <c r="J89">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>9</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90" s="120">
+        <v>3.0129999999999999</v>
+      </c>
+      <c r="D90">
+        <v>8</v>
+      </c>
+      <c r="E90">
+        <v>68</v>
+      </c>
+      <c r="H90">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I90">
+        <v>15</v>
+      </c>
+      <c r="J90">
+        <v>15.08</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>10</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91" s="120">
+        <v>3.01</v>
+      </c>
+      <c r="D91">
+        <v>8</v>
+      </c>
+      <c r="E91">
+        <v>68</v>
+      </c>
+      <c r="H91">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I91">
+        <v>16</v>
+      </c>
+      <c r="J91">
+        <v>322.77</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>11</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92" s="120">
+        <v>3.012</v>
+      </c>
+      <c r="D92">
+        <v>8</v>
+      </c>
+      <c r="E92">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>12</v>
+      </c>
+      <c r="B93">
+        <v>1</v>
+      </c>
+      <c r="C93" s="120">
+        <v>3.0089999999999999</v>
+      </c>
+      <c r="D93">
+        <v>8</v>
+      </c>
+      <c r="E93">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>13</v>
+      </c>
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94" s="120">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="D94">
+        <v>8</v>
+      </c>
+      <c r="E94">
+        <v>71.709999999999994</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>14</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95" s="120">
+        <v>3.0019999999999998</v>
+      </c>
+      <c r="D95">
+        <v>8</v>
+      </c>
+      <c r="E95">
+        <v>73.05</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>15</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96" s="120">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="D96">
+        <v>8</v>
+      </c>
+      <c r="E96">
+        <v>129.68</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>16</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97" s="120">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="D97">
+        <v>9</v>
+      </c>
+      <c r="E97">
+        <v>17.21</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>17</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98" s="120">
+        <v>3.016</v>
+      </c>
+      <c r="D98">
+        <v>9</v>
+      </c>
+      <c r="E98">
+        <v>21.12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>18</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99" s="120">
+        <v>3.0169999999999999</v>
+      </c>
+      <c r="D99">
+        <v>9</v>
+      </c>
+      <c r="E99">
+        <v>5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>19</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100" s="120">
+        <v>3.0179999999999998</v>
+      </c>
+      <c r="D100">
+        <v>9</v>
+      </c>
+      <c r="E100">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>20</v>
+      </c>
+      <c r="B101">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C101" s="120">
+        <v>3.0209999999999999</v>
+      </c>
+      <c r="D101">
+        <v>13</v>
+      </c>
+      <c r="E101">
+        <v>15.62</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>21</v>
+      </c>
+      <c r="B102">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C102" s="120" t="s">
+        <v>129</v>
+      </c>
+      <c r="D102">
+        <v>14</v>
+      </c>
+      <c r="E102">
+        <v>140.80000000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>22</v>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103" s="120">
+        <v>3.0059999999999998</v>
+      </c>
+      <c r="D103">
+        <v>15</v>
+      </c>
+      <c r="E103">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>23</v>
+      </c>
+      <c r="B104">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C104" s="120">
+        <v>3.0939999999999999</v>
+      </c>
+      <c r="D104">
+        <v>15</v>
+      </c>
+      <c r="E104">
+        <v>15.07</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>24</v>
+      </c>
+      <c r="B105">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C105" s="120">
+        <v>3.085</v>
+      </c>
+      <c r="D105">
+        <v>16</v>
+      </c>
+      <c r="E105">
+        <v>13.16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>25</v>
+      </c>
+      <c r="B106">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C106" s="120">
+        <v>2.0790000000000002</v>
+      </c>
+      <c r="D106">
+        <v>16</v>
+      </c>
+      <c r="E106">
+        <v>310.88</v>
+      </c>
+      <c r="F106">
+        <v>322.77</v>
+      </c>
+      <c r="G106">
+        <f>F106-E105</f>
+        <v>309.60999999999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="G80:J80"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="G31:J31"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="3">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="47.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="37"/>
+      <c r="B1" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="39"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="41"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="28">
+        <v>1</v>
+      </c>
+      <c r="E3" s="29">
+        <f>'4.СКБспец'!E9</f>
+        <v>637</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="E4" s="31">
+        <f>D4*E3</f>
+        <v>2866.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="35">
+        <v>0.15</v>
+      </c>
+      <c r="E5" s="36">
+        <f>D5*E3</f>
+        <v>95.55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="122" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="122" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="122" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="122" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="122" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="122">
+        <v>1</v>
+      </c>
+      <c r="B3" s="135">
+        <v>1</v>
+      </c>
+      <c r="C3" s="135">
+        <v>1.024</v>
+      </c>
+      <c r="D3" s="135">
+        <v>6</v>
+      </c>
+      <c r="E3" s="135">
+        <v>11.62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="122">
+        <v>2</v>
+      </c>
+      <c r="B4" s="135">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C4" s="135">
+        <v>2.081</v>
+      </c>
+      <c r="D4" s="135">
+        <v>13</v>
+      </c>
+      <c r="E4" s="135">
+        <v>228.82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="122">
+        <v>3</v>
+      </c>
+      <c r="B5" s="122">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C5" s="122">
+        <v>3.0209999999999999</v>
+      </c>
+      <c r="D5" s="122">
+        <v>13</v>
+      </c>
+      <c r="E5" s="122">
+        <v>13.72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="122">
+        <v>4</v>
+      </c>
+      <c r="B6" s="122">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C6" s="122" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="122">
+        <v>14</v>
+      </c>
+      <c r="E6" s="122">
+        <v>110.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="122">
+        <v>5</v>
+      </c>
+      <c r="B7" s="135">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C7" s="135">
+        <v>3.085</v>
+      </c>
+      <c r="D7" s="135">
+        <v>16</v>
+      </c>
+      <c r="E7" s="135">
+        <v>13.16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="122">
+        <v>6</v>
+      </c>
+      <c r="B8" s="135">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C8" s="135">
+        <v>2.0790000000000002</v>
+      </c>
+      <c r="D8" s="135">
+        <v>16</v>
+      </c>
+      <c r="E8" s="135">
+        <v>258.88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="135"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="135" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="135">
+        <f>SUM(E3:E8)</f>
+        <v>637</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/school_lublino/vor_lublino_ceiling.xlsx
+++ b/school_lublino/vor_lublino_ceiling.xlsx
@@ -9,25 +9,27 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" tabRatio="603" firstSheet="3" activeTab="7"/>
+    <workbookView xWindow="23265" yWindow="5565" windowWidth="5535" windowHeight="6105" tabRatio="790" firstSheet="6" activeTab="9"/>
   </bookViews>
   <sheets>
-    <sheet name="ВОР 2 э. шт." sheetId="8" r:id="rId1"/>
-    <sheet name="Спец 2 э. шт." sheetId="7" r:id="rId2"/>
-    <sheet name="Спец 2 эт. шлиф." sheetId="9" r:id="rId3"/>
-    <sheet name="1этВор" sheetId="10" r:id="rId4"/>
-    <sheet name="1эт спец" sheetId="11" r:id="rId5"/>
-    <sheet name="Вор2Вып" sheetId="12" r:id="rId6"/>
+    <sheet name="ВОР 2 э. шт." sheetId="8" state="hidden" r:id="rId1"/>
+    <sheet name="Спец 2 э. шт." sheetId="7" state="hidden" r:id="rId2"/>
+    <sheet name="Спец 2 эт. шлиф." sheetId="9" state="hidden" r:id="rId3"/>
+    <sheet name="1этВор" sheetId="10" state="hidden" r:id="rId4"/>
+    <sheet name="1эт спец" sheetId="11" state="hidden" r:id="rId5"/>
+    <sheet name="Вор2Вып" sheetId="12" state="hidden" r:id="rId6"/>
     <sheet name="Общий" sheetId="13" r:id="rId7"/>
-    <sheet name="4.СКБвор" sheetId="15" r:id="rId8"/>
-    <sheet name="4.СКБспец" sheetId="14" r:id="rId9"/>
+    <sheet name="4.СКБвор" sheetId="15" state="hidden" r:id="rId8"/>
+    <sheet name="4.СКБспец" sheetId="14" state="hidden" r:id="rId9"/>
+    <sheet name="5.Кр-Пт" sheetId="17" r:id="rId10"/>
+    <sheet name="ПокрПом" sheetId="16" r:id="rId11"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="148">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -430,6 +432,51 @@
   </si>
   <si>
     <t xml:space="preserve">Ведомость работ и используемых материалов </t>
+  </si>
+  <si>
+    <t>Лакокрасочные работы СКБ / окраска потолков / в 2 слоя</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Огнестойкая краска КМ-0, Краска НГ</t>
+  </si>
+  <si>
+    <t>Сумма:</t>
+  </si>
+  <si>
+    <t>тип П-13, П-16</t>
+  </si>
+  <si>
+    <t>тип П-6</t>
+  </si>
+  <si>
+    <t>тип П-14</t>
+  </si>
+  <si>
+    <t>П-7, П-10</t>
+  </si>
+  <si>
+    <t>Тип П-12, П-15</t>
+  </si>
+  <si>
+    <t>Тип</t>
+  </si>
+  <si>
+    <t>Тип-9</t>
+  </si>
+  <si>
+    <t>Матовая огнестойкая краска для высококачественной отделки стен и потолков, RAL 9003 (белый) КМ0/НГ</t>
+  </si>
+  <si>
+    <t>матовая огнестойкая краска, Краска НГ RAL 7016 КМ0/НГ</t>
+  </si>
+  <si>
+    <t>матовая водно-дисперсионная краска RAL 7044 (серый шелк) КМ1/Г1</t>
+  </si>
+  <si>
+    <t>матовая огнестойкая краска RAL 9003 (белый) КМ0/НГ</t>
+  </si>
+  <si>
+    <t>ANTEGA СТРОИТЕЛЬ RAL 9003 (белый) КМ0/НГ</t>
   </si>
 </sst>
 </file>
@@ -511,12 +558,36 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="34">
@@ -973,7 +1044,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1323,6 +1394,59 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1353,8 +1477,92 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1431,7 +1639,7 @@
   <autoFilter ref="A2:E28">
     <filterColumn colId="3">
       <filters>
-        <filter val="6"/>
+        <filter val="12"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1454,8 +1662,7 @@
   <autoFilter ref="A32:E76">
     <filterColumn colId="3">
       <filters>
-        <filter val="6"/>
-        <filter val="13"/>
+        <filter val="15"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1478,10 +1685,7 @@
   <autoFilter ref="A81:E106">
     <filterColumn colId="3">
       <filters>
-        <filter val="13"/>
-        <filter val="14"/>
-        <filter val="16"/>
-        <filter val="6"/>
+        <filter val="15"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2008,6 +2212,1785 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="8" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" style="131" customWidth="1"/>
+    <col min="2" max="2" width="47.42578125" style="190" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="131" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="131" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="131" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="132"/>
+    <col min="7" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="133"/>
+      <c r="B1" s="134" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="135"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="137"/>
+    </row>
+    <row r="2" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="138" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="135" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="135" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="136" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="139" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="140" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="129" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="130">
+        <v>1</v>
+      </c>
+      <c r="F3" s="141">
+        <f>ПокрПом!E28</f>
+        <v>196.11999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="140" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="130">
+        <v>0.3</v>
+      </c>
+      <c r="F4" s="141">
+        <f>E4*F3</f>
+        <v>58.835999999999991</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="140" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="130">
+        <v>0.15</v>
+      </c>
+      <c r="F5" s="141">
+        <f>E5*F3</f>
+        <v>29.417999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="124">
+        <v>2</v>
+      </c>
+      <c r="B6" s="189" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="124" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="124">
+        <v>1</v>
+      </c>
+      <c r="F6" s="137">
+        <f>ПокрПом!E39</f>
+        <v>631.62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="124">
+        <v>2.1</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="124"/>
+      <c r="D7" s="124" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="124">
+        <v>0.15</v>
+      </c>
+      <c r="F7" s="141">
+        <f>E7*F6</f>
+        <v>94.742999999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="124">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="124">
+        <v>0.3</v>
+      </c>
+      <c r="F8" s="141">
+        <f>E8*F6</f>
+        <v>189.48599999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="124">
+        <v>3</v>
+      </c>
+      <c r="B9" s="189" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="124" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="124" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="124">
+        <v>1</v>
+      </c>
+      <c r="F9" s="137">
+        <f>ПокрПом!E66</f>
+        <v>2468.63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="124">
+        <v>3.1</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="124">
+        <v>0.3</v>
+      </c>
+      <c r="F10" s="141">
+        <f>E10*F9</f>
+        <v>740.58900000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="124">
+        <v>3.2</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="124">
+        <v>0.15</v>
+      </c>
+      <c r="F11" s="141">
+        <f>E11*F9</f>
+        <v>370.29450000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="124">
+        <v>4</v>
+      </c>
+      <c r="B12" s="189" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="124" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="124" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="124">
+        <v>1</v>
+      </c>
+      <c r="F12" s="137">
+        <f>ПокрПом!E70</f>
+        <v>132.71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="124">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="124"/>
+      <c r="D13" s="124" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="124">
+        <v>0.15</v>
+      </c>
+      <c r="F13" s="141">
+        <f>E13*F12</f>
+        <v>19.906500000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="124">
+        <v>4.2</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="124"/>
+      <c r="D14" s="124" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="124">
+        <v>0.3</v>
+      </c>
+      <c r="F14" s="141">
+        <f>E14*F12</f>
+        <v>39.813000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="124">
+        <v>5</v>
+      </c>
+      <c r="B15" s="189" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="124" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="124" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="124">
+        <v>1</v>
+      </c>
+      <c r="F15" s="137">
+        <f>ПокрПом!E82</f>
+        <v>456.19999999999993</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="124">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" s="124"/>
+      <c r="D16" s="124" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="124">
+        <v>0.3</v>
+      </c>
+      <c r="F16" s="141">
+        <f>E16*F15</f>
+        <v>136.85999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="124">
+        <v>5.2</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="124"/>
+      <c r="D17" s="124" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="124">
+        <v>0.15</v>
+      </c>
+      <c r="F17" s="141">
+        <f>E17*F15</f>
+        <v>68.429999999999993</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="124">
+        <v>6</v>
+      </c>
+      <c r="B18" s="189" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="124" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" s="124" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="124">
+        <v>1</v>
+      </c>
+      <c r="F18" s="137">
+        <f>ПокрПом!E98</f>
+        <v>106.37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="124">
+        <v>6.1</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="124"/>
+      <c r="D19" s="124" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="124">
+        <v>0.15</v>
+      </c>
+      <c r="F19" s="141">
+        <f>E19*F18</f>
+        <v>15.955500000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="124">
+        <v>6.2</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20" s="124"/>
+      <c r="D20" s="124" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="124">
+        <v>0.3</v>
+      </c>
+      <c r="F20" s="141">
+        <f>E20*F18</f>
+        <v>31.911000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="8" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:E98"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="154" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="155" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="156" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="157" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="156" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="158" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="159">
+        <v>1</v>
+      </c>
+      <c r="B3" s="159">
+        <v>1</v>
+      </c>
+      <c r="C3" s="162">
+        <v>1.034</v>
+      </c>
+      <c r="D3" s="159">
+        <v>9</v>
+      </c>
+      <c r="E3" s="159">
+        <v>17.12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="159">
+        <v>2</v>
+      </c>
+      <c r="B4" s="159">
+        <v>1</v>
+      </c>
+      <c r="C4" s="162">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="D4" s="159">
+        <v>9</v>
+      </c>
+      <c r="E4" s="159">
+        <v>21.34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="159">
+        <v>3</v>
+      </c>
+      <c r="B5" s="159">
+        <v>1</v>
+      </c>
+      <c r="C5" s="162">
+        <v>1.036</v>
+      </c>
+      <c r="D5" s="159">
+        <v>9</v>
+      </c>
+      <c r="E5" s="159">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="159">
+        <v>4</v>
+      </c>
+      <c r="B6" s="159">
+        <v>1</v>
+      </c>
+      <c r="C6" s="162">
+        <v>1.0369999999999999</v>
+      </c>
+      <c r="D6" s="159">
+        <v>9</v>
+      </c>
+      <c r="E6" s="159">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="187"/>
+      <c r="B7" s="187"/>
+      <c r="C7" s="188"/>
+      <c r="D7" s="159" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="159">
+        <f>SUM(E3:E6)</f>
+        <v>47.56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="154" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="154"/>
+      <c r="C8" s="154"/>
+      <c r="D8" s="154"/>
+      <c r="E8" s="154"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="155" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="156" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="157" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="156" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" s="158" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="159">
+        <v>5</v>
+      </c>
+      <c r="B10" s="159">
+        <v>1</v>
+      </c>
+      <c r="C10" s="162">
+        <v>2.0139999999999998</v>
+      </c>
+      <c r="D10" s="159">
+        <v>9</v>
+      </c>
+      <c r="E10" s="159">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="159">
+        <v>6</v>
+      </c>
+      <c r="B11" s="159">
+        <v>1</v>
+      </c>
+      <c r="C11" s="162">
+        <v>2.0150000000000001</v>
+      </c>
+      <c r="D11" s="159">
+        <v>9</v>
+      </c>
+      <c r="E11" s="159">
+        <v>20.93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="159">
+        <v>7</v>
+      </c>
+      <c r="B12" s="159">
+        <v>1</v>
+      </c>
+      <c r="C12" s="162">
+        <v>2.016</v>
+      </c>
+      <c r="D12" s="159">
+        <v>9</v>
+      </c>
+      <c r="E12" s="159">
+        <v>5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="159">
+        <v>8</v>
+      </c>
+      <c r="B13" s="159">
+        <v>1</v>
+      </c>
+      <c r="C13" s="162">
+        <v>2.0169999999999999</v>
+      </c>
+      <c r="D13" s="159">
+        <v>9</v>
+      </c>
+      <c r="E13" s="159">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="159">
+        <v>9</v>
+      </c>
+      <c r="B14" s="159">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C14" s="162">
+        <v>2.09</v>
+      </c>
+      <c r="D14" s="159">
+        <v>9</v>
+      </c>
+      <c r="E14" s="159">
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="159">
+        <v>10</v>
+      </c>
+      <c r="B15" s="159">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C15" s="162">
+        <v>2.0910000000000002</v>
+      </c>
+      <c r="D15" s="159">
+        <v>9</v>
+      </c>
+      <c r="E15" s="159">
+        <v>10.63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="159">
+        <v>11</v>
+      </c>
+      <c r="B16" s="159">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C16" s="162">
+        <v>2.0950000000000002</v>
+      </c>
+      <c r="D16" s="159">
+        <v>9</v>
+      </c>
+      <c r="E16" s="159">
+        <v>8.4600000000000009</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="159">
+        <v>12</v>
+      </c>
+      <c r="B17" s="159">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C17" s="162">
+        <v>2.1</v>
+      </c>
+      <c r="D17" s="159">
+        <v>9</v>
+      </c>
+      <c r="E17" s="159">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="159">
+        <v>13</v>
+      </c>
+      <c r="B18" s="159">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C18" s="162">
+        <v>2.1040000000000001</v>
+      </c>
+      <c r="D18" s="159">
+        <v>9</v>
+      </c>
+      <c r="E18" s="159">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="159">
+        <v>14</v>
+      </c>
+      <c r="B19" s="159">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C19" s="162">
+        <v>2.1070000000000002</v>
+      </c>
+      <c r="D19" s="159">
+        <v>9</v>
+      </c>
+      <c r="E19" s="159">
+        <v>8.14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="160"/>
+      <c r="B20" s="160"/>
+      <c r="C20" s="161"/>
+      <c r="D20" s="159" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" s="159">
+        <f>SUM(E10:E19)</f>
+        <v>102.31999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="154" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="154"/>
+      <c r="C21" s="154"/>
+      <c r="D21" s="154"/>
+      <c r="E21" s="154"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="155" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="156" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="157" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" s="156" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" s="158" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="159">
+        <v>15</v>
+      </c>
+      <c r="B23" s="159">
+        <v>1</v>
+      </c>
+      <c r="C23" s="162">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="D23" s="159">
+        <v>9</v>
+      </c>
+      <c r="E23" s="159">
+        <v>17.21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="159">
+        <v>16</v>
+      </c>
+      <c r="B24" s="159">
+        <v>1</v>
+      </c>
+      <c r="C24" s="162">
+        <v>3.016</v>
+      </c>
+      <c r="D24" s="159">
+        <v>9</v>
+      </c>
+      <c r="E24" s="159">
+        <v>20.87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="159">
+        <v>17</v>
+      </c>
+      <c r="B25" s="159">
+        <v>1</v>
+      </c>
+      <c r="C25" s="162">
+        <v>3.0169999999999999</v>
+      </c>
+      <c r="D25" s="159">
+        <v>9</v>
+      </c>
+      <c r="E25" s="159">
+        <v>5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="159">
+        <v>18</v>
+      </c>
+      <c r="B26" s="159">
+        <v>1</v>
+      </c>
+      <c r="C26" s="162">
+        <v>3.0179999999999998</v>
+      </c>
+      <c r="D26" s="159">
+        <v>9</v>
+      </c>
+      <c r="E26" s="159">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="160"/>
+      <c r="B27" s="160"/>
+      <c r="C27" s="160"/>
+      <c r="D27" s="159" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" s="159">
+        <f>SUM(E23:E26)</f>
+        <v>46.24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="160"/>
+      <c r="B28" s="160"/>
+      <c r="C28" s="160"/>
+      <c r="D28" s="159" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" s="159">
+        <f>E27+E20+E7</f>
+        <v>196.11999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="163" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" s="163"/>
+      <c r="C30" s="163"/>
+      <c r="D30" s="163"/>
+      <c r="E30" s="163"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="164" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="165" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="166" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="165" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" s="167" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="168">
+        <v>1</v>
+      </c>
+      <c r="B32" s="168">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C32" s="169">
+        <v>2.081</v>
+      </c>
+      <c r="D32" s="168">
+        <v>13</v>
+      </c>
+      <c r="E32" s="168">
+        <v>295.85000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="184" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="185"/>
+      <c r="C33" s="185"/>
+      <c r="D33" s="185"/>
+      <c r="E33" s="186"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="164" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="165" t="s">
+        <v>123</v>
+      </c>
+      <c r="C34" s="166" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" s="165" t="s">
+        <v>125</v>
+      </c>
+      <c r="E34" s="167" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="168">
+        <v>2</v>
+      </c>
+      <c r="B35" s="168">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C35" s="169">
+        <v>3.0209999999999999</v>
+      </c>
+      <c r="D35" s="168">
+        <v>13</v>
+      </c>
+      <c r="E35" s="168">
+        <v>15.37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="168">
+        <v>3</v>
+      </c>
+      <c r="B36" s="168">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C36" s="169">
+        <v>3.085</v>
+      </c>
+      <c r="D36" s="168">
+        <v>16</v>
+      </c>
+      <c r="E36" s="168">
+        <v>13.08</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="168">
+        <v>4</v>
+      </c>
+      <c r="B37" s="168">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C37" s="169">
+        <v>2.0790000000000002</v>
+      </c>
+      <c r="D37" s="168">
+        <v>16</v>
+      </c>
+      <c r="E37" s="168">
+        <v>307.32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="168"/>
+      <c r="B38" s="168"/>
+      <c r="C38" s="168"/>
+      <c r="D38" s="168" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="168">
+        <f>SUM(E35:E37)</f>
+        <v>335.77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="168"/>
+      <c r="B39" s="168"/>
+      <c r="C39" s="168"/>
+      <c r="D39" s="168" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="168">
+        <f>E38+E32</f>
+        <v>631.62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="177" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" s="177"/>
+      <c r="C42" s="177"/>
+      <c r="D42" s="177"/>
+      <c r="E42" s="177"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="178" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="179" t="s">
+        <v>123</v>
+      </c>
+      <c r="C43" s="180" t="s">
+        <v>124</v>
+      </c>
+      <c r="D43" s="179" t="s">
+        <v>125</v>
+      </c>
+      <c r="E43" s="181" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="182">
+        <v>1</v>
+      </c>
+      <c r="B44" s="182">
+        <v>1</v>
+      </c>
+      <c r="C44" s="183">
+        <v>1.024</v>
+      </c>
+      <c r="D44" s="182">
+        <v>6</v>
+      </c>
+      <c r="E44" s="182">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="182">
+        <v>2</v>
+      </c>
+      <c r="B45" s="182">
+        <v>1</v>
+      </c>
+      <c r="C45" s="183">
+        <v>1.026</v>
+      </c>
+      <c r="D45" s="182">
+        <v>6</v>
+      </c>
+      <c r="E45" s="182">
+        <v>191.68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="182">
+        <v>3</v>
+      </c>
+      <c r="B46" s="182">
+        <v>1</v>
+      </c>
+      <c r="C46" s="183">
+        <v>1.0389999999999999</v>
+      </c>
+      <c r="D46" s="182">
+        <v>6</v>
+      </c>
+      <c r="E46" s="182">
+        <v>149.69999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="182">
+        <v>4</v>
+      </c>
+      <c r="B47" s="182">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C47" s="183">
+        <v>1.0449999999999999</v>
+      </c>
+      <c r="D47" s="182">
+        <v>6</v>
+      </c>
+      <c r="E47" s="182">
+        <v>161.78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="182">
+        <v>5</v>
+      </c>
+      <c r="B48" s="182">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C48" s="183">
+        <v>1.046</v>
+      </c>
+      <c r="D48" s="182">
+        <v>6</v>
+      </c>
+      <c r="E48" s="182">
+        <v>161.15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="182">
+        <v>6</v>
+      </c>
+      <c r="B49" s="182">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C49" s="183">
+        <v>1.0529999999999999</v>
+      </c>
+      <c r="D49" s="182">
+        <v>6</v>
+      </c>
+      <c r="E49" s="182">
+        <v>443.48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="182"/>
+      <c r="B50" s="182"/>
+      <c r="C50" s="183"/>
+      <c r="D50" s="182" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="182">
+        <f>SUM(E44:E49)</f>
+        <v>1121.4099999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="177" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" s="177"/>
+      <c r="C51" s="177"/>
+      <c r="D51" s="177"/>
+      <c r="E51" s="177"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="178" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="179" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="180" t="s">
+        <v>124</v>
+      </c>
+      <c r="D52" s="179" t="s">
+        <v>125</v>
+      </c>
+      <c r="E52" s="181" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="182">
+        <v>7</v>
+      </c>
+      <c r="B53" s="182">
+        <v>1</v>
+      </c>
+      <c r="C53" s="183">
+        <v>2.004</v>
+      </c>
+      <c r="D53" s="182">
+        <v>6</v>
+      </c>
+      <c r="E53" s="182">
+        <v>158.71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="182">
+        <v>8</v>
+      </c>
+      <c r="B54" s="182">
+        <v>1</v>
+      </c>
+      <c r="C54" s="183">
+        <v>2.012</v>
+      </c>
+      <c r="D54" s="182">
+        <v>6</v>
+      </c>
+      <c r="E54" s="182">
+        <v>144.29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="182">
+        <v>9</v>
+      </c>
+      <c r="B55" s="182">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C55" s="183">
+        <v>2.0750000000000002</v>
+      </c>
+      <c r="D55" s="182">
+        <v>6</v>
+      </c>
+      <c r="E55" s="182">
+        <v>79.790000000000006</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="182">
+        <v>10</v>
+      </c>
+      <c r="B56" s="182">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C56" s="183">
+        <v>2.08</v>
+      </c>
+      <c r="D56" s="182">
+        <v>6</v>
+      </c>
+      <c r="E56" s="182">
+        <v>165.74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="182">
+        <v>11</v>
+      </c>
+      <c r="B57" s="182">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C57" s="183">
+        <v>2.0819999999999999</v>
+      </c>
+      <c r="D57" s="182">
+        <v>6</v>
+      </c>
+      <c r="E57" s="182">
+        <v>32.630000000000003</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="182"/>
+      <c r="B58" s="182"/>
+      <c r="C58" s="183"/>
+      <c r="D58" s="182" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="182">
+        <f>SUM(E53:E57)</f>
+        <v>581.16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="177" t="s">
+        <v>108</v>
+      </c>
+      <c r="B59" s="177"/>
+      <c r="C59" s="177"/>
+      <c r="D59" s="177"/>
+      <c r="E59" s="177"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="178" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="179" t="s">
+        <v>123</v>
+      </c>
+      <c r="C60" s="180" t="s">
+        <v>124</v>
+      </c>
+      <c r="D60" s="179" t="s">
+        <v>125</v>
+      </c>
+      <c r="E60" s="181" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="182">
+        <v>12</v>
+      </c>
+      <c r="B61" s="182">
+        <v>1</v>
+      </c>
+      <c r="C61" s="183">
+        <v>3.0139999999999998</v>
+      </c>
+      <c r="D61" s="182">
+        <v>6</v>
+      </c>
+      <c r="E61" s="182">
+        <v>148.61000000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="182">
+        <v>13</v>
+      </c>
+      <c r="B62" s="182">
+        <v>1</v>
+      </c>
+      <c r="C62" s="183">
+        <v>3.0049999999999999</v>
+      </c>
+      <c r="D62" s="182">
+        <v>6</v>
+      </c>
+      <c r="E62" s="182">
+        <v>238.37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="182">
+        <v>14</v>
+      </c>
+      <c r="B63" s="182">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C63" s="183">
+        <v>3.02</v>
+      </c>
+      <c r="D63" s="182">
+        <v>6</v>
+      </c>
+      <c r="E63" s="182">
+        <v>137.72999999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="182">
+        <v>15</v>
+      </c>
+      <c r="B64" s="182">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C64" s="182">
+        <v>3.0190000000000001</v>
+      </c>
+      <c r="D64" s="182">
+        <v>6</v>
+      </c>
+      <c r="E64" s="182">
+        <v>241.35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="182"/>
+      <c r="B65" s="182"/>
+      <c r="C65" s="182"/>
+      <c r="D65" s="182" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" s="182">
+        <f>SUM(E60:E64)</f>
+        <v>766.06000000000006</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="182"/>
+      <c r="B66" s="182"/>
+      <c r="C66" s="182"/>
+      <c r="D66" s="182" t="s">
+        <v>93</v>
+      </c>
+      <c r="E66" s="182">
+        <f>E65+E58+E50</f>
+        <v>2468.63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="142" t="s">
+        <v>108</v>
+      </c>
+      <c r="B68" s="142"/>
+      <c r="C68" s="142"/>
+      <c r="D68" s="142"/>
+      <c r="E68" s="142"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="123" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E69" s="126" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="127">
+        <v>1</v>
+      </c>
+      <c r="B70" s="127">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C70" s="128" t="s">
+        <v>129</v>
+      </c>
+      <c r="D70" s="127">
+        <v>14</v>
+      </c>
+      <c r="E70" s="127">
+        <v>132.71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="170" t="s">
+        <v>108</v>
+      </c>
+      <c r="B73" s="170"/>
+      <c r="C73" s="170"/>
+      <c r="D73" s="170"/>
+      <c r="E73" s="170"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="171" t="s">
+        <v>0</v>
+      </c>
+      <c r="B74" s="172" t="s">
+        <v>123</v>
+      </c>
+      <c r="C74" s="173" t="s">
+        <v>124</v>
+      </c>
+      <c r="D74" s="172" t="s">
+        <v>125</v>
+      </c>
+      <c r="E74" s="174" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="175">
+        <v>1</v>
+      </c>
+      <c r="B75" s="175">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C75" s="176">
+        <v>1.04</v>
+      </c>
+      <c r="D75" s="175">
+        <v>10</v>
+      </c>
+      <c r="E75" s="175">
+        <v>215.72</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="175">
+        <v>2</v>
+      </c>
+      <c r="B76" s="175">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C76" s="176">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="D76" s="175">
+        <v>10</v>
+      </c>
+      <c r="E76" s="175">
+        <v>61.99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="175">
+        <v>3</v>
+      </c>
+      <c r="B77" s="175">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C77" s="176">
+        <v>1.044</v>
+      </c>
+      <c r="D77" s="175">
+        <v>10</v>
+      </c>
+      <c r="E77" s="175">
+        <v>14.14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="175"/>
+      <c r="B78" s="175"/>
+      <c r="C78" s="176"/>
+      <c r="D78" s="175" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78" s="175">
+        <f>SUM(E75:E77)</f>
+        <v>291.84999999999997</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="170" t="s">
+        <v>108</v>
+      </c>
+      <c r="B79" s="170"/>
+      <c r="C79" s="170"/>
+      <c r="D79" s="170"/>
+      <c r="E79" s="170"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="171" t="s">
+        <v>0</v>
+      </c>
+      <c r="B80" s="172" t="s">
+        <v>123</v>
+      </c>
+      <c r="C80" s="173" t="s">
+        <v>124</v>
+      </c>
+      <c r="D80" s="172" t="s">
+        <v>125</v>
+      </c>
+      <c r="E80" s="174" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="175">
+        <v>4</v>
+      </c>
+      <c r="B81" s="175">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C81" s="176">
+        <v>2.085</v>
+      </c>
+      <c r="D81" s="175">
+        <v>7</v>
+      </c>
+      <c r="E81" s="175">
+        <v>164.35</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="175"/>
+      <c r="B82" s="175"/>
+      <c r="C82" s="175"/>
+      <c r="D82" s="175" t="s">
+        <v>93</v>
+      </c>
+      <c r="E82" s="175">
+        <f>E81+E78</f>
+        <v>456.19999999999993</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="154" t="s">
+        <v>108</v>
+      </c>
+      <c r="B85" s="154"/>
+      <c r="C85" s="154"/>
+      <c r="D85" s="154"/>
+      <c r="E85" s="154"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="155" t="s">
+        <v>0</v>
+      </c>
+      <c r="B86" s="156" t="s">
+        <v>123</v>
+      </c>
+      <c r="C86" s="157" t="s">
+        <v>124</v>
+      </c>
+      <c r="D86" s="156" t="s">
+        <v>125</v>
+      </c>
+      <c r="E86" s="158" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="159">
+        <v>1</v>
+      </c>
+      <c r="B87" s="159">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C87" s="159">
+        <v>1.054</v>
+      </c>
+      <c r="D87" s="159">
+        <v>12</v>
+      </c>
+      <c r="E87" s="159">
+        <v>56.35</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="154" t="s">
+        <v>108</v>
+      </c>
+      <c r="B88" s="154"/>
+      <c r="C88" s="154"/>
+      <c r="D88" s="154"/>
+      <c r="E88" s="154"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="155" t="s">
+        <v>0</v>
+      </c>
+      <c r="B89" s="156" t="s">
+        <v>123</v>
+      </c>
+      <c r="C89" s="157" t="s">
+        <v>124</v>
+      </c>
+      <c r="D89" s="156" t="s">
+        <v>125</v>
+      </c>
+      <c r="E89" s="158" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="159">
+        <v>2</v>
+      </c>
+      <c r="B90" s="159">
+        <v>1</v>
+      </c>
+      <c r="C90" s="162">
+        <v>2.0049999999999999</v>
+      </c>
+      <c r="D90" s="159">
+        <v>15</v>
+      </c>
+      <c r="E90" s="159">
+        <v>13.31</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="159">
+        <v>3</v>
+      </c>
+      <c r="B91" s="159">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C91" s="162">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="D91" s="159">
+        <v>15</v>
+      </c>
+      <c r="E91" s="159">
+        <v>8.02</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="159"/>
+      <c r="B92" s="159"/>
+      <c r="C92" s="162"/>
+      <c r="D92" s="159" t="s">
+        <v>15</v>
+      </c>
+      <c r="E92" s="159">
+        <f>SUM(E90:E91)</f>
+        <v>21.33</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="154" t="s">
+        <v>108</v>
+      </c>
+      <c r="B93" s="154"/>
+      <c r="C93" s="154"/>
+      <c r="D93" s="154"/>
+      <c r="E93" s="154"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="155" t="s">
+        <v>0</v>
+      </c>
+      <c r="B94" s="156" t="s">
+        <v>123</v>
+      </c>
+      <c r="C94" s="157" t="s">
+        <v>124</v>
+      </c>
+      <c r="D94" s="156" t="s">
+        <v>125</v>
+      </c>
+      <c r="E94" s="158" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="159">
+        <v>4</v>
+      </c>
+      <c r="B95" s="159">
+        <v>1</v>
+      </c>
+      <c r="C95" s="162">
+        <v>3.0059999999999998</v>
+      </c>
+      <c r="D95" s="159">
+        <v>15</v>
+      </c>
+      <c r="E95" s="159">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="159">
+        <v>5</v>
+      </c>
+      <c r="B96" s="159">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C96" s="162">
+        <v>3.0939999999999999</v>
+      </c>
+      <c r="D96" s="159">
+        <v>15</v>
+      </c>
+      <c r="E96" s="159">
+        <v>15.07</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="159"/>
+      <c r="B97" s="159"/>
+      <c r="C97" s="159"/>
+      <c r="D97" s="159" t="s">
+        <v>15</v>
+      </c>
+      <c r="E97" s="159">
+        <f>SUM(E95:E96)</f>
+        <v>28.689999999999998</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="159"/>
+      <c r="B98" s="159"/>
+      <c r="C98" s="159"/>
+      <c r="D98" s="159" t="s">
+        <v>93</v>
+      </c>
+      <c r="E98" s="159">
+        <f>E97+E92+E87</f>
+        <v>106.37</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A79:E79"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K35"/>
@@ -2023,25 +4006,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="142" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
       <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="124" t="s">
+      <c r="A2" s="143" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="125"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="126"/>
+      <c r="B2" s="144"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="145"/>
       <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -2818,18 +4801,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="146" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
     </row>
     <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="128" t="s">
+      <c r="A2" s="147" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="128"/>
-      <c r="C2" s="128"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
     </row>
     <row r="3" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -4005,19 +5988,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="148" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="131"/>
-      <c r="G1" s="132" t="s">
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="150"/>
+      <c r="G1" s="151" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="134"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="153"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="117" t="s">
@@ -4103,7 +6086,7 @@
         <v>23.92</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -4132,7 +6115,7 @@
         <v>352.16</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -4164,7 +6147,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -4197,7 +6180,7 @@
         <v>3.0150000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -4230,7 +6213,7 @@
         <v>3.016</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -4263,7 +6246,7 @@
         <v>3.0169999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -4648,13 +6631,20 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C27" s="120">
-        <v>1.1439999999999999</v>
+        <v>1.044</v>
       </c>
       <c r="D27">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E27">
+        <v>14.14</v>
+      </c>
+      <c r="K27">
+        <f>296.76-E25-E26</f>
+        <v>14.29999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -4673,19 +6663,19 @@
       <c r="F28" s="121"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="129" t="s">
+      <c r="A31" s="148" t="s">
         <v>108</v>
       </c>
-      <c r="B31" s="130"/>
-      <c r="C31" s="130"/>
-      <c r="D31" s="130"/>
-      <c r="E31" s="131"/>
-      <c r="G31" s="132" t="s">
+      <c r="B31" s="149"/>
+      <c r="C31" s="149"/>
+      <c r="D31" s="149"/>
+      <c r="E31" s="150"/>
+      <c r="G31" s="151" t="s">
         <v>108</v>
       </c>
-      <c r="H31" s="133"/>
-      <c r="I31" s="133"/>
-      <c r="J31" s="134"/>
+      <c r="H31" s="152"/>
+      <c r="I31" s="152"/>
+      <c r="J31" s="153"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="117" t="s">
@@ -4803,7 +6793,7 @@
         <v>180.8</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>14</v>
       </c>
@@ -4829,7 +6819,7 @@
         <v>306.63</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>43</v>
       </c>
@@ -4985,7 +6975,7 @@
         <v>299.02</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>15</v>
       </c>
@@ -5156,7 +7146,7 @@
         <v>113.65</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>17</v>
       </c>
@@ -5173,7 +7163,7 @@
         <v>79.790000000000006</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>18</v>
       </c>
@@ -5190,7 +7180,7 @@
         <v>170.56</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>16</v>
       </c>
@@ -5207,7 +7197,7 @@
         <v>32.630000000000003</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>42</v>
       </c>
@@ -5561,7 +7551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>44</v>
       </c>
@@ -5579,19 +7569,19 @@
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="129" t="s">
+      <c r="A80" s="148" t="s">
         <v>108</v>
       </c>
-      <c r="B80" s="130"/>
-      <c r="C80" s="130"/>
-      <c r="D80" s="130"/>
-      <c r="E80" s="131"/>
-      <c r="G80" s="132" t="s">
+      <c r="B80" s="149"/>
+      <c r="C80" s="149"/>
+      <c r="D80" s="149"/>
+      <c r="E80" s="150"/>
+      <c r="G80" s="151" t="s">
         <v>108</v>
       </c>
-      <c r="H80" s="133"/>
-      <c r="I80" s="133"/>
-      <c r="J80" s="134"/>
+      <c r="H80" s="152"/>
+      <c r="I80" s="152"/>
+      <c r="J80" s="153"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="117" t="s">
@@ -5648,7 +7638,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2</v>
       </c>
@@ -5674,7 +7664,7 @@
         <v>388.9</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>3</v>
       </c>
@@ -5700,7 +7690,7 @@
         <v>380.9</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>4</v>
       </c>
@@ -5726,7 +7716,7 @@
         <v>748.81</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>5</v>
       </c>
@@ -6035,7 +8025,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>20</v>
       </c>
@@ -6052,7 +8042,7 @@
         <v>15.62</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>21</v>
       </c>
@@ -6069,7 +8059,7 @@
         <v>140.80000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>22</v>
       </c>
@@ -6086,7 +8076,7 @@
         <v>13.62</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>23</v>
       </c>
@@ -6103,7 +8093,7 @@
         <v>15.07</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>24</v>
       </c>
@@ -6120,7 +8110,7 @@
         <v>13.16</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>25</v>
       </c>
@@ -6275,13 +8265,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="151" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="134"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="153"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="122" t="s">
@@ -6304,16 +8294,16 @@
       <c r="A3" s="122">
         <v>1</v>
       </c>
-      <c r="B3" s="135">
-        <v>1</v>
-      </c>
-      <c r="C3" s="135">
+      <c r="B3" s="125">
+        <v>1</v>
+      </c>
+      <c r="C3" s="125">
         <v>1.024</v>
       </c>
-      <c r="D3" s="135">
+      <c r="D3" s="125">
         <v>6</v>
       </c>
-      <c r="E3" s="135">
+      <c r="E3" s="125">
         <v>11.62</v>
       </c>
     </row>
@@ -6321,16 +8311,16 @@
       <c r="A4" s="122">
         <v>2</v>
       </c>
-      <c r="B4" s="135">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C4" s="135">
+      <c r="B4" s="125">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C4" s="125">
         <v>2.081</v>
       </c>
-      <c r="D4" s="135">
+      <c r="D4" s="125">
         <v>13</v>
       </c>
-      <c r="E4" s="135">
+      <c r="E4" s="125">
         <v>228.82</v>
       </c>
     </row>
@@ -6372,16 +8362,16 @@
       <c r="A7" s="122">
         <v>5</v>
       </c>
-      <c r="B7" s="135">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C7" s="135">
+      <c r="B7" s="125">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C7" s="125">
         <v>3.085</v>
       </c>
-      <c r="D7" s="135">
+      <c r="D7" s="125">
         <v>16</v>
       </c>
-      <c r="E7" s="135">
+      <c r="E7" s="125">
         <v>13.16</v>
       </c>
     </row>
@@ -6389,27 +8379,27 @@
       <c r="A8" s="122">
         <v>6</v>
       </c>
-      <c r="B8" s="135">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C8" s="135">
+      <c r="B8" s="125">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C8" s="125">
         <v>2.0790000000000002</v>
       </c>
-      <c r="D8" s="135">
+      <c r="D8" s="125">
         <v>16</v>
       </c>
-      <c r="E8" s="135">
+      <c r="E8" s="125">
         <v>258.88</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="135"/>
-      <c r="B9" s="135"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="135" t="s">
+      <c r="A9" s="125"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125" t="s">
         <v>130</v>
       </c>
-      <c r="E9" s="135">
+      <c r="E9" s="125">
         <f>SUM(E3:E8)</f>
         <v>637</v>
       </c>
